--- a/source/bin/excel/marathon.xlsx
+++ b/source/bin/excel/marathon.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\雀魂策划\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595E6F4F-5F9C-4091-89C2-65F0FDF6FABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9523A970-5E85-4DEA-BDEF-4A0D7F30115D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="-120" windowWidth="28035" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="6" r:id="rId1"/>
@@ -20,17 +20,28 @@
     <sheet name="marathon_reward" sheetId="5" r:id="rId5"/>
     <sheet name="marathon_item_group" sheetId="2" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="144">
   <si>
     <t>##</t>
   </si>
@@ -99,9 +110,6 @@
     <t>must_fever_count</t>
   </si>
   <si>
-    <t>必定出现福牌次数</t>
-  </si>
-  <si>
     <t>finish_hands_check</t>
   </si>
   <si>
@@ -451,11 +459,70 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ban_fever</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>福牌必定不会出现</t>
+    <t>final_mode</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>终局模式，福牌必定不会出现，不使用仓检</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>point_item_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡萝卜id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练度id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>distance_item_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单轮游戏每N距离获得1训练度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单轮游戏获得训练度数量上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_distance_reward</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>distance_reward_rate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无效牌位置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wall_empty_pos[0]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wall_empty_pos[1]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wall_empty_pos[2]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fevertime期间的道具类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fever_item_type</t>
+  </si>
+  <si>
+    <t>必定出现福牌次数</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +530,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -814,94 +881,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FB2019-08C3-4067-AA3D-CD4CE1C819B1}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.125" customWidth="1"/>
     <col min="4" max="4" width="21.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -912,8 +979,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V7"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
@@ -924,14 +991,20 @@
     <col min="7" max="7" width="31.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.875" customWidth="1"/>
     <col min="9" max="9" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="12.875" customWidth="1"/>
+    <col min="16" max="16" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.875" customWidth="1"/>
+    <col min="20" max="20" width="15.125" customWidth="1"/>
+    <col min="21" max="22" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -939,49 +1012,67 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M1" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="N1" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="O1" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="P1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>132</v>
+      </c>
+      <c r="R1" t="s">
+        <v>136</v>
+      </c>
+      <c r="S1" t="s">
+        <v>135</v>
+      </c>
+      <c r="T1" t="s">
+        <v>138</v>
+      </c>
+      <c r="U1" t="s">
+        <v>139</v>
+      </c>
+      <c r="V1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -989,49 +1080,61 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
       <c r="G2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="O2" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="P2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>131</v>
+      </c>
+      <c r="R2" t="s">
+        <v>133</v>
+      </c>
+      <c r="S2" t="s">
+        <v>134</v>
+      </c>
+      <c r="T2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1080,8 +1183,20 @@
       <c r="P3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q3" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3" t="s">
+        <v>6</v>
+      </c>
+      <c r="S3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1204,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22">
       <c r="B5">
         <v>260201</v>
       </c>
@@ -1100,13 +1215,13 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="F5">
         <v>30</v>
       </c>
       <c r="G5">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>15</v>
@@ -1115,32 +1230,50 @@
         <v>7</v>
       </c>
       <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1001</v>
+      </c>
+      <c r="L5">
+        <v>2001</v>
+      </c>
+      <c r="M5">
+        <v>3001</v>
+      </c>
+      <c r="N5">
+        <v>4001</v>
+      </c>
+      <c r="O5">
+        <v>30900098</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
+        <v>30900099</v>
+      </c>
+      <c r="R5">
         <v>100</v>
       </c>
-      <c r="K5">
-        <v>50</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1001</v>
-      </c>
-      <c r="N5">
-        <v>2001</v>
-      </c>
-      <c r="O5">
-        <v>3001</v>
-      </c>
-      <c r="P5">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="S5">
+        <v>10</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22">
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
@@ -1152,23 +1285,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542471BF-90FE-4958-AD73-98965FFF44A7}">
-  <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O51"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.875" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.25" customWidth="1"/>
+    <col min="8" max="8" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1182,75 +1317,87 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" t="s">
         <v>59</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>60</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>61</v>
       </c>
-      <c r="L2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1290,15 +1437,21 @@
       <c r="M3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N3" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5">
         <v>1001</v>
@@ -1307,75 +1460,87 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>90</v>
       </c>
       <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>15</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
         <v>100</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>100</v>
-      </c>
-      <c r="J5">
+      <c r="L5">
         <v>80</v>
       </c>
-      <c r="K5">
-        <v>60</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
       <c r="M5">
+        <v>25</v>
+      </c>
+      <c r="N5">
+        <v>40</v>
+      </c>
+      <c r="O5">
         <v>4001</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15">
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F6">
+        <v>25</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>100</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
         <v>80</v>
       </c>
-      <c r="K6">
-        <v>60</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
       <c r="M6">
+        <v>25</v>
+      </c>
+      <c r="N6">
+        <v>40</v>
+      </c>
+      <c r="O6">
         <v>4001</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15">
       <c r="B7">
         <v>1001</v>
       </c>
@@ -1386,34 +1551,40 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F7">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
         <v>100</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
-      <c r="J7">
+      <c r="L7">
         <v>80</v>
       </c>
-      <c r="K7">
-        <v>60</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
       <c r="M7">
+        <v>25</v>
+      </c>
+      <c r="N7">
+        <v>40</v>
+      </c>
+      <c r="O7">
         <v>4001</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15">
       <c r="B8">
         <v>1001</v>
       </c>
@@ -1421,489 +1592,1931 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8">
         <v>75</v>
       </c>
       <c r="F8">
+        <v>25</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>100</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
+      <c r="L8">
+        <v>80</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
+      </c>
+      <c r="N8">
+        <v>35</v>
+      </c>
+      <c r="O8">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9">
+        <v>1001</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>70</v>
+      </c>
+      <c r="F9">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>94</v>
+      </c>
+      <c r="L9">
+        <v>75</v>
+      </c>
+      <c r="M9">
+        <v>25</v>
+      </c>
+      <c r="N9">
+        <v>35</v>
+      </c>
+      <c r="O9">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10">
+        <v>1001</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>17</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+      <c r="F10">
+        <v>25</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>15</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>88</v>
+      </c>
+      <c r="L10">
+        <v>70</v>
+      </c>
+      <c r="M10">
+        <v>25</v>
+      </c>
+      <c r="N10">
+        <v>35</v>
+      </c>
+      <c r="O10">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11">
+        <v>1001</v>
+      </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>63</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>15</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>82</v>
+      </c>
+      <c r="L11">
+        <v>65</v>
+      </c>
+      <c r="M11">
+        <v>25</v>
+      </c>
+      <c r="N11">
+        <v>30</v>
+      </c>
+      <c r="O11">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12">
+        <v>1001</v>
+      </c>
+      <c r="C12">
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>23</v>
+      </c>
+      <c r="E12">
+        <v>61</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>76</v>
+      </c>
+      <c r="L12">
+        <v>60</v>
+      </c>
+      <c r="M12">
+        <v>25</v>
+      </c>
+      <c r="N12">
+        <v>30</v>
+      </c>
+      <c r="O12">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13">
+        <v>1001</v>
+      </c>
+      <c r="C13">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>26</v>
+      </c>
+      <c r="E13">
+        <v>59</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>70</v>
+      </c>
+      <c r="L13">
+        <v>55</v>
+      </c>
+      <c r="M13">
+        <v>25</v>
+      </c>
+      <c r="N13">
+        <v>30</v>
+      </c>
+      <c r="O13">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="B14">
+        <v>1001</v>
+      </c>
+      <c r="C14">
+        <v>27</v>
+      </c>
+      <c r="D14">
+        <v>29</v>
+      </c>
+      <c r="E14">
+        <v>57</v>
+      </c>
+      <c r="F14">
+        <v>50</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>64</v>
+      </c>
+      <c r="L14">
+        <v>50</v>
+      </c>
+      <c r="M14">
+        <v>25</v>
+      </c>
+      <c r="N14">
+        <v>30</v>
+      </c>
+      <c r="O14">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="B15">
+        <v>1001</v>
+      </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>32</v>
+      </c>
+      <c r="E15">
+        <v>55</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>58</v>
+      </c>
+      <c r="L15">
+        <v>45</v>
+      </c>
+      <c r="M15">
+        <v>25</v>
+      </c>
+      <c r="N15">
+        <v>25</v>
+      </c>
+      <c r="O15">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16">
+        <v>1001</v>
+      </c>
+      <c r="C16">
+        <v>33</v>
+      </c>
+      <c r="D16">
+        <v>35</v>
+      </c>
+      <c r="E16">
+        <v>53</v>
+      </c>
+      <c r="F16">
+        <v>75</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>52</v>
+      </c>
+      <c r="L16">
+        <v>40</v>
+      </c>
+      <c r="M16">
+        <v>25</v>
+      </c>
+      <c r="N16">
+        <v>25</v>
+      </c>
+      <c r="O16">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17">
+        <v>1001</v>
+      </c>
+      <c r="C17">
+        <v>36</v>
+      </c>
+      <c r="D17">
+        <v>38</v>
+      </c>
+      <c r="E17">
+        <v>51</v>
+      </c>
+      <c r="F17">
+        <v>75</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>10</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>46</v>
+      </c>
+      <c r="L17">
+        <v>35</v>
+      </c>
+      <c r="M17">
+        <v>25</v>
+      </c>
+      <c r="N17">
+        <v>25</v>
+      </c>
+      <c r="O17">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="B18">
+        <v>1001</v>
+      </c>
+      <c r="C18">
+        <v>39</v>
+      </c>
+      <c r="D18">
+        <v>41</v>
+      </c>
+      <c r="E18">
+        <v>49</v>
+      </c>
+      <c r="F18">
+        <v>75</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>10</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>40</v>
+      </c>
+      <c r="L18">
+        <v>30</v>
+      </c>
+      <c r="M18">
+        <v>25</v>
+      </c>
+      <c r="N18">
+        <v>25</v>
+      </c>
+      <c r="O18">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15">
+      <c r="B19">
+        <v>1001</v>
+      </c>
+      <c r="C19">
+        <v>42</v>
+      </c>
+      <c r="D19">
+        <v>44</v>
+      </c>
+      <c r="E19">
+        <v>47</v>
+      </c>
+      <c r="F19">
+        <v>75</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>10</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>33</v>
+      </c>
+      <c r="L19">
+        <v>30</v>
+      </c>
+      <c r="M19">
+        <v>25</v>
+      </c>
+      <c r="N19">
+        <v>20</v>
+      </c>
+      <c r="O19">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20">
+        <v>1001</v>
+      </c>
+      <c r="C20">
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <v>47</v>
+      </c>
+      <c r="E20">
+        <v>45</v>
+      </c>
+      <c r="F20">
+        <v>75</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>10</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>30</v>
+      </c>
+      <c r="L20">
+        <v>29</v>
+      </c>
+      <c r="M20">
+        <v>25</v>
+      </c>
+      <c r="N20">
+        <v>20</v>
+      </c>
+      <c r="O20">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21">
+        <v>1001</v>
+      </c>
+      <c r="C21">
+        <v>48</v>
+      </c>
+      <c r="D21">
+        <v>50</v>
+      </c>
+      <c r="E21">
+        <v>44</v>
+      </c>
+      <c r="F21">
+        <v>75</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>27</v>
+      </c>
+      <c r="L21">
+        <v>28</v>
+      </c>
+      <c r="M21">
+        <v>25</v>
+      </c>
+      <c r="N21">
+        <v>20</v>
+      </c>
+      <c r="O21">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22">
+        <v>1001</v>
+      </c>
+      <c r="C22">
+        <v>51</v>
+      </c>
+      <c r="D22">
+        <v>53</v>
+      </c>
+      <c r="E22">
+        <v>43</v>
+      </c>
+      <c r="F22">
+        <v>75</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>24</v>
+      </c>
+      <c r="L22">
+        <v>27</v>
+      </c>
+      <c r="M22">
+        <v>25</v>
+      </c>
+      <c r="N22">
+        <v>20</v>
+      </c>
+      <c r="O22">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23">
+        <v>1001</v>
+      </c>
+      <c r="C23">
+        <v>54</v>
+      </c>
+      <c r="D23">
+        <v>56</v>
+      </c>
+      <c r="E23">
+        <v>42</v>
+      </c>
+      <c r="F23">
         <v>100</v>
       </c>
-      <c r="J8">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>10</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>21</v>
+      </c>
+      <c r="L23">
+        <v>26</v>
+      </c>
+      <c r="M23">
+        <v>25</v>
+      </c>
+      <c r="N23">
+        <v>20</v>
+      </c>
+      <c r="O23">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="B24">
+        <v>1001</v>
+      </c>
+      <c r="C24">
+        <v>57</v>
+      </c>
+      <c r="D24">
+        <v>59</v>
+      </c>
+      <c r="E24">
+        <v>41</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>10</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>18</v>
+      </c>
+      <c r="L24">
+        <v>25</v>
+      </c>
+      <c r="M24">
+        <v>25</v>
+      </c>
+      <c r="N24">
+        <v>15</v>
+      </c>
+      <c r="O24">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="B25">
+        <v>1001</v>
+      </c>
+      <c r="C25">
+        <v>60</v>
+      </c>
+      <c r="D25">
+        <v>62</v>
+      </c>
+      <c r="E25">
+        <v>40</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>15</v>
+      </c>
+      <c r="L25">
+        <v>24</v>
+      </c>
+      <c r="M25">
+        <v>25</v>
+      </c>
+      <c r="N25">
+        <v>15</v>
+      </c>
+      <c r="O25">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15">
+      <c r="B26">
+        <v>1001</v>
+      </c>
+      <c r="C26">
+        <v>63</v>
+      </c>
+      <c r="D26">
+        <v>65</v>
+      </c>
+      <c r="E26">
+        <v>39</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>12</v>
+      </c>
+      <c r="L26">
+        <v>23</v>
+      </c>
+      <c r="M26">
+        <v>25</v>
+      </c>
+      <c r="N26">
+        <v>15</v>
+      </c>
+      <c r="O26">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="B27">
+        <v>1001</v>
+      </c>
+      <c r="C27">
+        <v>66</v>
+      </c>
+      <c r="D27">
+        <v>68</v>
+      </c>
+      <c r="E27">
+        <v>38</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>9</v>
+      </c>
+      <c r="L27">
+        <v>22</v>
+      </c>
+      <c r="M27">
+        <v>25</v>
+      </c>
+      <c r="N27">
+        <v>10</v>
+      </c>
+      <c r="O27">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="B28">
+        <v>1001</v>
+      </c>
+      <c r="C28">
+        <v>69</v>
+      </c>
+      <c r="D28">
+        <v>71</v>
+      </c>
+      <c r="E28">
+        <v>37</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>6</v>
+      </c>
+      <c r="L28">
+        <v>21</v>
+      </c>
+      <c r="M28">
+        <v>25</v>
+      </c>
+      <c r="N28">
+        <v>10</v>
+      </c>
+      <c r="O28">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29">
+        <v>1001</v>
+      </c>
+      <c r="C29">
+        <v>72</v>
+      </c>
+      <c r="D29">
+        <v>74</v>
+      </c>
+      <c r="E29">
+        <v>36</v>
+      </c>
+      <c r="F29">
+        <v>125</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>3</v>
+      </c>
+      <c r="L29">
+        <v>20</v>
+      </c>
+      <c r="M29">
+        <v>25</v>
+      </c>
+      <c r="N29">
+        <v>10</v>
+      </c>
+      <c r="O29">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="B30">
+        <v>1001</v>
+      </c>
+      <c r="C30">
+        <v>75</v>
+      </c>
+      <c r="D30">
+        <v>77</v>
+      </c>
+      <c r="E30">
+        <v>35</v>
+      </c>
+      <c r="F30">
+        <v>125</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>19</v>
+      </c>
+      <c r="M30">
+        <v>15</v>
+      </c>
+      <c r="N30">
+        <v>10</v>
+      </c>
+      <c r="O30">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="B31">
+        <v>1001</v>
+      </c>
+      <c r="C31">
+        <v>78</v>
+      </c>
+      <c r="D31">
         <v>80</v>
       </c>
-      <c r="K8">
-        <v>60</v>
-      </c>
-      <c r="L8">
+      <c r="E31">
+        <v>34</v>
+      </c>
+      <c r="F31">
+        <v>125</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>17</v>
+      </c>
+      <c r="M31">
+        <v>15</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15">
+      <c r="B32">
+        <v>1001</v>
+      </c>
+      <c r="C32">
+        <v>81</v>
+      </c>
+      <c r="D32">
+        <v>83</v>
+      </c>
+      <c r="E32">
+        <v>33</v>
+      </c>
+      <c r="F32">
+        <v>125</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>15</v>
+      </c>
+      <c r="M32">
+        <v>15</v>
+      </c>
+      <c r="N32">
+        <v>5</v>
+      </c>
+      <c r="O32">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15">
+      <c r="B33">
+        <v>1001</v>
+      </c>
+      <c r="C33">
+        <v>84</v>
+      </c>
+      <c r="D33">
+        <v>86</v>
+      </c>
+      <c r="E33">
+        <v>32</v>
+      </c>
+      <c r="F33">
+        <v>125</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>13</v>
+      </c>
+      <c r="M33">
+        <v>15</v>
+      </c>
+      <c r="N33">
+        <v>5</v>
+      </c>
+      <c r="O33">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15">
+      <c r="B34">
+        <v>1001</v>
+      </c>
+      <c r="C34">
+        <v>87</v>
+      </c>
+      <c r="D34">
+        <v>89</v>
+      </c>
+      <c r="E34">
+        <v>31</v>
+      </c>
+      <c r="F34">
+        <v>125</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>11</v>
+      </c>
+      <c r="M34">
+        <v>15</v>
+      </c>
+      <c r="N34">
+        <v>5</v>
+      </c>
+      <c r="O34">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15">
+      <c r="B35">
+        <v>1001</v>
+      </c>
+      <c r="C35">
+        <v>90</v>
+      </c>
+      <c r="D35">
+        <v>93</v>
+      </c>
+      <c r="E35">
+        <v>30</v>
+      </c>
+      <c r="F35">
+        <v>125</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>9</v>
+      </c>
+      <c r="M35">
+        <v>15</v>
+      </c>
+      <c r="N35">
+        <v>5</v>
+      </c>
+      <c r="O35">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15">
+      <c r="B36">
+        <v>1001</v>
+      </c>
+      <c r="C36">
+        <v>94</v>
+      </c>
+      <c r="D36">
+        <v>97</v>
+      </c>
+      <c r="E36">
+        <v>30</v>
+      </c>
+      <c r="F36">
+        <v>125</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>7</v>
+      </c>
+      <c r="M36">
+        <v>15</v>
+      </c>
+      <c r="N36">
+        <v>5</v>
+      </c>
+      <c r="O36">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15">
+      <c r="B37">
+        <v>1001</v>
+      </c>
+      <c r="C37">
+        <v>98</v>
+      </c>
+      <c r="D37">
+        <v>101</v>
+      </c>
+      <c r="E37">
+        <v>30</v>
+      </c>
+      <c r="F37">
+        <v>150</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>5</v>
+      </c>
+      <c r="M37">
+        <v>15</v>
+      </c>
+      <c r="N37">
+        <v>5</v>
+      </c>
+      <c r="O37">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15">
+      <c r="B38">
+        <v>1001</v>
+      </c>
+      <c r="C38">
+        <v>102</v>
+      </c>
+      <c r="D38">
+        <v>105</v>
+      </c>
+      <c r="E38">
+        <v>30</v>
+      </c>
+      <c r="F38">
+        <v>150</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>3</v>
+      </c>
+      <c r="M38">
+        <v>15</v>
+      </c>
+      <c r="N38">
+        <v>5</v>
+      </c>
+      <c r="O38">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15">
+      <c r="B39">
+        <v>1001</v>
+      </c>
+      <c r="C39">
+        <v>106</v>
+      </c>
+      <c r="D39">
+        <v>109</v>
+      </c>
+      <c r="E39">
+        <v>30</v>
+      </c>
+      <c r="F39">
+        <v>150</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
         <v>1</v>
       </c>
-      <c r="M8">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B9">
-        <v>1001</v>
-      </c>
-      <c r="C9">
-        <v>11</v>
-      </c>
-      <c r="D9">
-        <v>12</v>
-      </c>
-      <c r="E9">
-        <v>60</v>
-      </c>
-      <c r="F9">
-        <v>125</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="M39">
+        <v>15</v>
+      </c>
+      <c r="N39">
+        <v>5</v>
+      </c>
+      <c r="O39">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15">
+      <c r="B40">
+        <v>1001</v>
+      </c>
+      <c r="C40">
+        <v>110</v>
+      </c>
+      <c r="D40">
+        <v>113</v>
+      </c>
+      <c r="E40">
+        <v>30</v>
+      </c>
+      <c r="F40">
+        <v>150</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>15</v>
+      </c>
+      <c r="N40">
+        <v>5</v>
+      </c>
+      <c r="O40">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15">
+      <c r="B41">
+        <v>1001</v>
+      </c>
+      <c r="C41">
+        <v>114</v>
+      </c>
+      <c r="D41">
+        <v>117</v>
+      </c>
+      <c r="E41">
+        <v>30</v>
+      </c>
+      <c r="F41">
+        <v>150</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>5</v>
+      </c>
+      <c r="N41">
+        <v>2</v>
+      </c>
+      <c r="O41">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15">
+      <c r="B42">
+        <v>1001</v>
+      </c>
+      <c r="C42">
+        <v>118</v>
+      </c>
+      <c r="D42">
+        <v>123</v>
+      </c>
+      <c r="E42">
+        <v>30</v>
+      </c>
+      <c r="F42">
+        <v>150</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>5</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
+      </c>
+      <c r="O42">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15">
+      <c r="B43">
+        <v>1001</v>
+      </c>
+      <c r="C43">
+        <v>124</v>
+      </c>
+      <c r="D43">
+        <v>130</v>
+      </c>
+      <c r="E43">
+        <v>30</v>
+      </c>
+      <c r="F43">
+        <v>150</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>5</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="O43">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15">
+      <c r="B44">
+        <v>1001</v>
+      </c>
+      <c r="C44">
+        <v>131</v>
+      </c>
+      <c r="D44">
+        <v>140</v>
+      </c>
+      <c r="E44">
+        <v>30</v>
+      </c>
+      <c r="F44">
+        <v>150</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>5</v>
+      </c>
+      <c r="N44">
+        <v>2</v>
+      </c>
+      <c r="O44">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15">
+      <c r="B45">
+        <v>1001</v>
+      </c>
+      <c r="C45">
+        <v>141</v>
+      </c>
+      <c r="D45">
+        <v>150</v>
+      </c>
+      <c r="E45">
+        <v>30</v>
+      </c>
+      <c r="F45">
+        <v>150</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>5</v>
+      </c>
+      <c r="N45">
+        <v>2</v>
+      </c>
+      <c r="O45">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15">
+      <c r="B46">
+        <v>1001</v>
+      </c>
+      <c r="C46">
+        <v>151</v>
+      </c>
+      <c r="D46">
+        <v>160</v>
+      </c>
+      <c r="E46">
+        <v>30</v>
+      </c>
+      <c r="F46">
+        <v>150</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
         <v>1</v>
       </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
-      <c r="J9">
-        <v>80</v>
-      </c>
-      <c r="K9">
-        <v>60</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B10">
-        <v>1001</v>
-      </c>
-      <c r="C10">
-        <v>13</v>
-      </c>
-      <c r="D10">
-        <v>20</v>
-      </c>
-      <c r="E10">
-        <v>60</v>
-      </c>
-      <c r="F10">
-        <v>125</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>100</v>
-      </c>
-      <c r="J10">
-        <v>80</v>
-      </c>
-      <c r="K10">
-        <v>60</v>
-      </c>
-      <c r="L10">
+      <c r="O46">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15">
+      <c r="B47">
+        <v>1001</v>
+      </c>
+      <c r="C47">
+        <v>161</v>
+      </c>
+      <c r="D47">
+        <v>170</v>
+      </c>
+      <c r="E47">
+        <v>30</v>
+      </c>
+      <c r="F47">
+        <v>150</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
         <v>1</v>
       </c>
-      <c r="M10">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B11">
-        <v>1001</v>
-      </c>
-      <c r="C11">
-        <v>21</v>
-      </c>
-      <c r="D11">
-        <v>23</v>
-      </c>
-      <c r="E11">
-        <v>55</v>
-      </c>
-      <c r="F11">
+      <c r="O47">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15">
+      <c r="B48">
+        <v>1001</v>
+      </c>
+      <c r="C48">
+        <v>171</v>
+      </c>
+      <c r="D48">
+        <v>200</v>
+      </c>
+      <c r="E48">
+        <v>30</v>
+      </c>
+      <c r="F48">
         <v>150</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
         <v>1</v>
       </c>
-      <c r="I11">
-        <v>80</v>
-      </c>
-      <c r="J11">
-        <v>60</v>
-      </c>
-      <c r="K11">
-        <v>40</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B12">
-        <v>1001</v>
-      </c>
-      <c r="C12">
-        <v>24</v>
-      </c>
-      <c r="D12">
-        <v>40</v>
-      </c>
-      <c r="E12">
-        <v>55</v>
-      </c>
-      <c r="F12">
+      <c r="O48">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15">
+      <c r="B49">
+        <v>1001</v>
+      </c>
+      <c r="C49">
+        <v>201</v>
+      </c>
+      <c r="D49">
+        <v>300</v>
+      </c>
+      <c r="E49">
+        <v>30</v>
+      </c>
+      <c r="F49">
         <v>150</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>80</v>
-      </c>
-      <c r="J12">
-        <v>60</v>
-      </c>
-      <c r="K12">
-        <v>40</v>
-      </c>
-      <c r="L12">
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
         <v>1</v>
       </c>
-      <c r="M12">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B13">
-        <v>1001</v>
-      </c>
-      <c r="C13">
-        <v>41</v>
-      </c>
-      <c r="D13">
-        <v>45</v>
-      </c>
-      <c r="E13">
-        <v>50</v>
-      </c>
-      <c r="F13">
-        <v>175</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
+      <c r="O49">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15">
+      <c r="B50">
+        <v>1001</v>
+      </c>
+      <c r="C50">
+        <v>301</v>
+      </c>
+      <c r="D50">
+        <v>400</v>
+      </c>
+      <c r="E50">
+        <v>30</v>
+      </c>
+      <c r="F50">
+        <v>150</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
         <v>1</v>
       </c>
-      <c r="I13">
-        <v>60</v>
-      </c>
-      <c r="J13">
-        <v>40</v>
-      </c>
-      <c r="K13">
-        <v>20</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>4002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B14">
-        <v>1001</v>
-      </c>
-      <c r="C14">
-        <v>46</v>
-      </c>
-      <c r="D14">
-        <v>70</v>
-      </c>
-      <c r="E14">
-        <v>50</v>
-      </c>
-      <c r="F14">
-        <v>175</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>60</v>
-      </c>
-      <c r="J14">
-        <v>40</v>
-      </c>
-      <c r="K14">
-        <v>20</v>
-      </c>
-      <c r="L14">
+      <c r="O50">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15">
+      <c r="B51">
+        <v>1001</v>
+      </c>
+      <c r="C51">
+        <v>401</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>30</v>
+      </c>
+      <c r="F51">
+        <v>150</v>
+      </c>
+      <c r="G51">
         <v>1</v>
       </c>
-      <c r="M14">
-        <v>4002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B15">
-        <v>1001</v>
-      </c>
-      <c r="C15">
-        <v>71</v>
-      </c>
-      <c r="D15">
-        <v>75</v>
-      </c>
-      <c r="E15">
-        <v>45</v>
-      </c>
-      <c r="F15">
-        <v>200</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>40</v>
-      </c>
-      <c r="J15">
-        <v>20</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>4002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B16">
-        <v>1001</v>
-      </c>
-      <c r="C16">
-        <v>76</v>
-      </c>
-      <c r="D16">
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <v>45</v>
-      </c>
-      <c r="F16">
-        <v>200</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>40</v>
-      </c>
-      <c r="J16">
-        <v>20</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>4002</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B17">
-        <v>1001</v>
-      </c>
-      <c r="C17">
-        <v>101</v>
-      </c>
-      <c r="D17">
-        <v>105</v>
-      </c>
-      <c r="E17">
-        <v>40</v>
-      </c>
-      <c r="F17">
-        <v>225</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>20</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>4003</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B18">
-        <v>1001</v>
-      </c>
-      <c r="C18">
-        <v>106</v>
-      </c>
-      <c r="D18">
-        <v>150</v>
-      </c>
-      <c r="E18">
-        <v>40</v>
-      </c>
-      <c r="F18">
-        <v>225</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>20</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>4003</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B19">
-        <v>1001</v>
-      </c>
-      <c r="C19">
-        <v>151</v>
-      </c>
-      <c r="D19">
-        <v>200</v>
-      </c>
-      <c r="E19">
-        <v>35</v>
-      </c>
-      <c r="F19">
-        <v>250</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>4003</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B20">
-        <v>1001</v>
-      </c>
-      <c r="C20">
-        <v>201</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>30</v>
-      </c>
-      <c r="F20">
-        <v>300</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
         <v>4003</v>
       </c>
     </row>
@@ -1916,13 +3529,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67331926-8CCA-4A21-B205-EA477CEA1DCF}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1930,33 +3543,33 @@
         <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1964,7 +3577,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -1973,143 +3586,143 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="B5">
         <v>2001</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="B6">
         <v>2001</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="B7">
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="B8">
         <v>2001</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="B9">
         <v>2001</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="B10">
         <v>2001</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="B11">
         <v>2001</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D11">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="B12">
         <v>2001</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D12">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="B13">
         <v>2001</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="B14">
         <v>2001</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14">
         <v>40</v>
@@ -2118,12 +3731,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="B15">
         <v>2001</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15">
         <v>60</v>
@@ -2132,12 +3745,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="B16">
         <v>2001</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D16">
         <v>80</v>
@@ -2146,12 +3759,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:5">
       <c r="B17">
         <v>2001</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -2160,12 +3773,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:5">
       <c r="B18">
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -2174,12 +3787,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:5">
       <c r="B19">
         <v>2001</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -2188,12 +3801,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:5">
       <c r="B20">
         <v>2001</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20">
         <v>80</v>
@@ -2202,12 +3815,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:5">
       <c r="B21">
         <v>2001</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21">
         <v>60</v>
@@ -2216,12 +3829,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:5">
       <c r="B22">
         <v>2001</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22">
         <v>40</v>
@@ -2230,12 +3843,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:5">
       <c r="B23">
         <v>2001</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23">
         <v>40</v>
@@ -2244,12 +3857,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:5">
       <c r="B24">
         <v>2001</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24">
         <v>60</v>
@@ -2258,12 +3871,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:5">
       <c r="B25">
         <v>2001</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25">
         <v>80</v>
@@ -2272,12 +3885,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:5">
       <c r="B26">
         <v>2001</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -2286,12 +3899,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:5">
       <c r="B27">
         <v>2001</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -2300,12 +3913,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:5">
       <c r="B28">
         <v>2001</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -2314,12 +3927,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:5">
       <c r="B29">
         <v>2001</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D29">
         <v>80</v>
@@ -2328,12 +3941,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:5">
       <c r="B30">
         <v>2001</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D30">
         <v>60</v>
@@ -2342,12 +3955,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:5">
       <c r="B31">
         <v>2001</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>40</v>
@@ -2356,102 +3969,102 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:5">
       <c r="B32">
         <v>2001</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D32">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
       <c r="B33">
         <v>2001</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D33">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
       <c r="B34">
         <v>2001</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
       <c r="B35">
         <v>2001</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
       <c r="B36">
         <v>2001</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D36">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
       <c r="B37">
         <v>2001</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D37">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
       <c r="B38">
         <v>2001</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D38">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2463,13 +4076,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6158AD8D-6620-4ACB-8BD9-FABEA80DE471}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="11.125" customWidth="1"/>
     <col min="5" max="5" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2477,27 +4090,27 @@
         <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
         <v>45</v>
       </c>
-      <c r="E1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2514,10 +4127,10 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2525,10 +4138,10 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5">
         <v>3001</v>
       </c>
@@ -2536,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2545,10 +4158,10 @@
         <v>2</v>
       </c>
       <c r="J5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6">
         <v>3001</v>
       </c>
@@ -2556,7 +4169,7 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2565,10 +4178,10 @@
         <v>3</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7">
         <v>3001</v>
       </c>
@@ -2576,19 +4189,19 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8">
         <v>3001</v>
       </c>
@@ -2596,7 +4209,7 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -2605,10 +4218,10 @@
         <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9">
         <v>3001</v>
       </c>
@@ -2619,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2631,9 +4244,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A9DFEC7-D486-49AC-AD2B-590578004E99}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2641,27 +4254,27 @@
         <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2675,10 +4288,10 @@
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2686,10 +4299,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="B5">
         <v>4001</v>
       </c>
@@ -2697,16 +4310,16 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="B6">
         <v>4001</v>
       </c>
@@ -2714,10 +4327,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="B7">
         <v>4002</v>
       </c>
@@ -2725,10 +4338,10 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="B8">
         <v>4002</v>
       </c>
@@ -2736,10 +4349,10 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="B9">
         <v>4003</v>
       </c>
